--- a/MM/61analitik_206/61analitik.xlsx
+++ b/MM/61analitik_206/61analitik.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\MM\61analitik_206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3908CC39-92A1-4F31-868F-796A0A078FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F188789-F416-425F-8AC1-E7370B760D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
-  <si>
-    <t>Öğrencinin;</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Ölçütler</t>
   </si>
@@ -34,18 +31,6 @@
     <t>Başarı Puanı</t>
   </si>
   <si>
-    <t>Görüşler ve Öneriler</t>
-  </si>
-  <si>
-    <t>Adı Soyadı :</t>
-  </si>
-  <si>
-    <t>Numarası :</t>
-  </si>
-  <si>
-    <t>Sınıfı :</t>
-  </si>
-  <si>
     <t>Veri Toplama</t>
   </si>
   <si>
@@ -133,10 +118,22 @@
     <t>Yorum Yapma</t>
   </si>
   <si>
-    <t>TOPLAM :</t>
-  </si>
-  <si>
     <t>6. TEMA - DEĞİŞİMİN MATEMATİĞİ (2) - ANALİTİK DERECELİ PUANLAMA ANAHTARI 6.1</t>
+  </si>
+  <si>
+    <t>Adı Soyadı</t>
+  </si>
+  <si>
+    <t>Numarası</t>
+  </si>
+  <si>
+    <t>Sınıfı</t>
+  </si>
+  <si>
+    <t>TOPLAM PUAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Bu form, öğrencinin performans görevini değerlendirmeniz amacıyla hazırlanmıştır. Öğrencinin belirtilen ölçütleri öğrenme durumunu en doğru yansıtan başarı düzeyini puanlayınız.</t>
   </si>
 </sst>
 </file>
@@ -178,7 +175,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -238,11 +235,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -290,8 +313,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,222 +659,207 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B1:G13"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="23.21875" style="3" customWidth="1"/>
     <col min="3" max="6" width="22.44140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="11.21875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="22.21875" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="17" t="s">
+    <row r="1" spans="2:7" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+    </row>
+    <row r="6" spans="2:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="C6" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="12"/>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="8" spans="2:7" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-    </row>
-    <row r="8" spans="2:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="12"/>
-      <c r="C9" s="7" t="s">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="2:7" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="2:8" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="2:7" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="2:8" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="2:7" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="2:8" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="2:7" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="2:8" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>31</v>
-      </c>
+    </row>
+    <row r="13" spans="2:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="2:8" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="B3:H3"/>
+  <mergeCells count="9">
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="G6:G7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.55118110236220474" bottom="0.55118110236220474" header="0" footer="0"/>
